--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BARA\Documents\UiPath\UCL_SignedInvoicePDFClassification_Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bara\UCL_SignedInvoicePDFClassification_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AE8023-4249-4385-BA71-2D63DA77DF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0B73AE-6BCA-4999-9691-A1902CE94F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="102">
   <si>
     <t>Name</t>
   </si>
@@ -353,6 +353,12 @@
   </si>
   <si>
     <t>Enable</t>
+  </si>
+  <si>
+    <t>RetryNumberUploadStorageItem</t>
+  </si>
+  <si>
+    <t>RetryNumberDeleteStorageItem</t>
   </si>
 </sst>
 </file>
@@ -740,13 +746,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1005"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5703125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="43.54296875" style="4" customWidth="1"/>
     <col min="2" max="2" width="43" style="4" customWidth="1"/>
-    <col min="3" max="3" width="81.42578125" style="4" customWidth="1"/>
-    <col min="4" max="26" width="8.7109375" style="4" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="4"/>
+    <col min="3" max="3" width="81.453125" style="4" customWidth="1"/>
+    <col min="4" max="26" width="8.7265625" style="4" customWidth="1"/>
+    <col min="27" max="16384" width="14.453125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -794,7 +800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.5">
       <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
@@ -816,7 +822,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="30">
+    <row r="5" spans="1:26" ht="29">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
@@ -865,7 +871,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="45">
+    <row r="10" spans="1:26" ht="43.5">
       <c r="A10" s="4" t="s">
         <v>47</v>
       </c>
@@ -876,7 +882,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" ht="14.5">
       <c r="A11" s="4" t="s">
         <v>89</v>
       </c>
@@ -976,7 +982,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="60">
+    <row r="24" spans="1:3" ht="58">
       <c r="A24" s="4" t="s">
         <v>73</v>
       </c>
@@ -987,7 +993,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="180">
+    <row r="25" spans="1:3" ht="159.5">
       <c r="A25" s="4" t="s">
         <v>72</v>
       </c>
@@ -2008,13 +2014,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z989"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Z991"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.42578125" customWidth="1"/>
-    <col min="4" max="26" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="75.453125" customWidth="1"/>
+    <col min="4" max="26" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -2051,7 +2057,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="30">
+    <row r="2" spans="1:26" ht="29">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2062,7 +2068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:26" ht="43.5">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -2191,19 +2197,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45">
+    <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="29">
+      <c r="A20" t="s">
         <v>39</v>
       </c>
-      <c r="B18" t="b">
+      <c r="B20" t="b">
         <v>0</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
@@ -3173,6 +3193,8 @@
     <row r="987" ht="14.25" customHeight="1"/>
     <row r="988" ht="14.25" customHeight="1"/>
     <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3182,12 +3204,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="60.28515625" customWidth="1"/>
-    <col min="4" max="26" width="65.42578125" customWidth="1"/>
+    <col min="1" max="1" width="31.81640625" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" customWidth="1"/>
+    <col min="3" max="3" width="60.26953125" customWidth="1"/>
+    <col min="4" max="26" width="65.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
